--- a/data/trans_dic/P2A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Hogares con personas con alguna limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,32; 32,88</t>
+          <t>16,53; 32,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,86; 43,97</t>
+          <t>25,24; 44,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,89; 46,52</t>
+          <t>27,3; 45,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68,37; 82,72</t>
+          <t>67,59; 82,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,11; 38,52</t>
+          <t>20,88; 38,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,41; 33,94</t>
+          <t>17,29; 34,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,06; 42,68</t>
+          <t>25,4; 42,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>59,55; 78,88</t>
+          <t>60,77; 79,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,41; 32,88</t>
+          <t>21,34; 32,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,39; 36,64</t>
+          <t>22,78; 35,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27,83; 40,77</t>
+          <t>28,49; 42,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,55; 78,63</t>
+          <t>66,4; 78,57</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,64; 47,77</t>
+          <t>28,24; 47,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,29; 46,9</t>
+          <t>26,6; 46,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,0; 38,78</t>
+          <t>22,57; 39,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69,42; 83,58</t>
+          <t>69,29; 83,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,71; 53,06</t>
+          <t>34,86; 53,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,52; 41,18</t>
+          <t>21,42; 39,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,84; 38,98</t>
+          <t>23,4; 38,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>75,84; 89,29</t>
+          <t>75,73; 90,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,24; 46,99</t>
+          <t>33,66; 47,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,65; 40,03</t>
+          <t>27,23; 40,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,47; 37,04</t>
+          <t>25,56; 36,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>74,76; 84,36</t>
+          <t>74,58; 84,23</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,93; 35,18</t>
+          <t>16,77; 35,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,7; 47,75</t>
+          <t>28,77; 47,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,39; 39,45</t>
+          <t>18,53; 39,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>75,64; 92,48</t>
+          <t>74,72; 92,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,82; 36,67</t>
+          <t>20,97; 35,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,5; 40,59</t>
+          <t>21,61; 40,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,95; 42,35</t>
+          <t>24,24; 42,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>67,08; 87,63</t>
+          <t>66,45; 87,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,08; 33,65</t>
+          <t>21,68; 32,83</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,21; 40,99</t>
+          <t>27,44; 40,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,03; 38,56</t>
+          <t>24,24; 38,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73,69; 87,78</t>
+          <t>73,96; 87,7</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,23; 39,82</t>
+          <t>27,67; 40,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,52; 44,93</t>
+          <t>31,28; 44,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,23; 41,49</t>
+          <t>29,64; 41,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71,2; 86,38</t>
+          <t>71,51; 86,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,95; 43,01</t>
+          <t>30,82; 43,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,98; 46,98</t>
+          <t>34,23; 46,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,73; 36,7</t>
+          <t>25,49; 36,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>70,33; 82,19</t>
+          <t>69,87; 82,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,99; 39,7</t>
+          <t>31,07; 39,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34,74; 43,65</t>
+          <t>34,61; 43,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,84; 36,87</t>
+          <t>28,93; 37,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72,34; 82,63</t>
+          <t>72,7; 82,76</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,39; 44,14</t>
+          <t>25,94; 45,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,73; 38,59</t>
+          <t>22,27; 37,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,04; 44,63</t>
+          <t>29,14; 44,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71,84; 83,94</t>
+          <t>72,0; 84,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,09; 53,81</t>
+          <t>35,86; 53,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,61; 48,06</t>
+          <t>31,37; 48,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,57; 51,35</t>
+          <t>35,32; 52,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>49,1; 73,87</t>
+          <t>52,79; 74,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34,35; 46,43</t>
+          <t>34,29; 46,78</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28,72; 40,53</t>
+          <t>29,25; 40,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34,75; 45,85</t>
+          <t>34,4; 45,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>61,74; 76,54</t>
+          <t>61,03; 76,77</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32,67; 51,69</t>
+          <t>32,9; 50,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,13; 48,86</t>
+          <t>27,59; 49,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,32; 45,63</t>
+          <t>25,46; 46,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>62,17; 80,8</t>
+          <t>61,34; 79,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31,44; 50,0</t>
+          <t>30,52; 50,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,63; 47,12</t>
+          <t>27,43; 46,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,45; 37,78</t>
+          <t>19,73; 37,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>75,17; 91,17</t>
+          <t>74,23; 91,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34,9; 48,15</t>
+          <t>34,98; 48,19</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30,57; 44,34</t>
+          <t>30,5; 45,36</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24,41; 38,42</t>
+          <t>25,31; 38,56</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>71,56; 83,46</t>
+          <t>71,91; 83,94</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29,94; 36,55</t>
+          <t>29,55; 36,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,76; 39,16</t>
+          <t>32,1; 39,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30,85; 37,71</t>
+          <t>31,11; 37,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74,24; 81,41</t>
+          <t>74,24; 81,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,89; 40,4</t>
+          <t>33,88; 40,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,71; 38,64</t>
+          <t>31,35; 38,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,26; 36,66</t>
+          <t>29,89; 36,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>71,03; 78,66</t>
+          <t>70,93; 78,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>32,84; 37,47</t>
+          <t>32,74; 37,39</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32,62; 37,64</t>
+          <t>32,78; 37,72</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31,38; 36,05</t>
+          <t>31,47; 36,29</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73,96; 79,26</t>
+          <t>73,82; 79,19</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas con alguna limitación (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>19426</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21023</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23384</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>79319</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>21119</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18173</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>25899</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>98604</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>40545</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>39195</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>49283</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>177923</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>13299; 26064</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15449; 27052</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17696; 29685</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>70602; 86223</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14956; 27588</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>12690; 25125</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>19879; 32922</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>83193; 109415</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>32450; 49576</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>30671; 47388</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>40768; 60208</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>160280; 189648</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>25691</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23922</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24831</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>72994</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>29490</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>20758</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>28739</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>79718</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>55181</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>44679</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>53570</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>152711</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>19400; 32930</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>17391; 30613</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>18574; 32531</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>65601; 79176</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>23525; 36297</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>14675; 26840</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>21774; 36008</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>72373; 86266</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>45834; 64548</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>36461; 54163</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>44829; 64072</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>141893; 160260</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>14562</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25004</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>13888</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>44280</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>23826</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20568</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>20052</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>50210</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>38388</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>45572</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>33940</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>94489</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>9770; 20705</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19141; 31823</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9119; 19599</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>38749; 47718</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>17602; 29965</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>14686; 27378</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>14789; 25623</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>42432; 55609</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>30822; 46674</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>36907; 54766</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>26720; 42010</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>85585; 101485</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>50150</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>50980</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>58569</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>172457</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>55314</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>65501</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>52875</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>167540</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>105464</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>116481</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>111444</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>339997</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>41862; 60842</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>42684; 60812</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>49146; 68986</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>156476; 188648</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>45781; 64270</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>55228; 74936</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>43552; 62829</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>152513; 180473</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>93172; 119356</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>103082; 130543</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>97390; 125286</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>317760; 361723</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>24012</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>27548</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>37060</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>93877</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>38312</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>36496</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>43533</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>107800</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>62324</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>64045</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>80593</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>201677</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>17927; 31103</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>20815; 35434</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>29599; 44873</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>85994; 100444</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>30316; 45130</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>28863; 44697</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>35025; 51724</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>85848; 120495</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>52682; 71884</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>54250; 74993</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>69055; 92285</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>172144; 216532</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>31794</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>20594</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>21413</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>49603</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>29149</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>27130</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>18403</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>61068</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>60944</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>47724</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>39817</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>110671</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>24634; 38029</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>14874; 26431</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>15361; 27802</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>42261; 54980</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>22095; 36290</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>20307; 34275</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>13379; 25256</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>53449; 65601</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>51518; 70965</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>39020; 58032</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>32437; 49423</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>101318; 118273</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>721</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1469</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>165636</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>169071</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>179144</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>512530</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>197211</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>188626</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>189502</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>564939</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>362847</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>357697</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>368647</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>1077469</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>148553; 182448</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>153090; 187837</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>163061; 197570</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>488587; 534937</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>179082; 213526</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>168473; 205540</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>170411; 207208</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>531423; 588572</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>337585; 385610</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>332509; 382626</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>344329; 397121</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>1038982; 1114522</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,53; 32,4</t>
+          <t>17,42; 32,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,24; 44,19</t>
+          <t>24,03; 44,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,3; 45,79</t>
+          <t>26,34; 47,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67,59; 82,54</t>
+          <t>68,32; 82,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,88; 38,51</t>
+          <t>20,81; 38,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,29; 34,23</t>
+          <t>16,97; 34,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,4; 42,07</t>
+          <t>24,87; 42,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>60,77; 79,92</t>
+          <t>61,78; 79,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,34; 32,6</t>
+          <t>21,09; 32,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,78; 35,2</t>
+          <t>22,95; 35,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,49; 42,08</t>
+          <t>28,13; 41,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,4; 78,57</t>
+          <t>66,62; 78,51</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,24; 47,94</t>
+          <t>27,88; 47,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,6; 46,82</t>
+          <t>25,86; 45,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,57; 39,52</t>
+          <t>22,91; 38,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69,29; 83,62</t>
+          <t>68,95; 83,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,86; 53,79</t>
+          <t>33,31; 53,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,42; 39,17</t>
+          <t>20,87; 39,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,4; 38,69</t>
+          <t>23,51; 39,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>75,73; 90,26</t>
+          <t>75,51; 89,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,66; 47,4</t>
+          <t>33,92; 47,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,23; 40,45</t>
+          <t>27,14; 40,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,56; 36,53</t>
+          <t>24,63; 36,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>74,58; 84,23</t>
+          <t>75,37; 84,89</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,77; 35,55</t>
+          <t>17,12; 35,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,77; 47,84</t>
+          <t>28,68; 47,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,53; 39,82</t>
+          <t>18,84; 40,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74,72; 92,01</t>
+          <t>76,88; 92,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,97; 35,7</t>
+          <t>21,34; 36,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,61; 40,28</t>
+          <t>22,51; 40,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,24; 42,0</t>
+          <t>23,63; 42,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>66,45; 87,09</t>
+          <t>68,03; 87,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,68; 32,83</t>
+          <t>21,54; 33,83</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,44; 40,72</t>
+          <t>27,76; 40,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,24; 38,11</t>
+          <t>23,63; 38,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73,96; 87,7</t>
+          <t>73,15; 87,39</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,67; 40,21</t>
+          <t>27,33; 39,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,28; 44,56</t>
+          <t>30,31; 43,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,64; 41,61</t>
+          <t>29,76; 41,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71,51; 86,21</t>
+          <t>71,66; 86,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,82; 43,26</t>
+          <t>30,71; 44,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,23; 46,44</t>
+          <t>34,64; 47,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,49; 36,77</t>
+          <t>25,34; 36,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>69,87; 82,68</t>
+          <t>69,02; 82,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,07; 39,8</t>
+          <t>30,67; 39,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34,61; 43,83</t>
+          <t>34,54; 43,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,93; 37,21</t>
+          <t>28,9; 37,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72,7; 82,76</t>
+          <t>72,6; 82,39</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,94; 45,0</t>
+          <t>26,69; 44,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,27; 37,92</t>
+          <t>22,03; 37,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,14; 44,18</t>
+          <t>29,15; 43,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72,0; 84,1</t>
+          <t>71,98; 84,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,86; 53,39</t>
+          <t>36,63; 53,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,37; 48,58</t>
+          <t>32,3; 49,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,32; 52,17</t>
+          <t>35,27; 52,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>52,79; 74,1</t>
+          <t>51,08; 74,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34,29; 46,78</t>
+          <t>34,05; 47,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,25; 40,44</t>
+          <t>29,57; 40,55</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34,4; 45,97</t>
+          <t>34,82; 46,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>61,03; 76,77</t>
+          <t>62,5; 77,25</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32,9; 50,79</t>
+          <t>32,48; 51,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,59; 49,03</t>
+          <t>27,73; 49,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,46; 46,08</t>
+          <t>25,85; 46,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61,34; 79,8</t>
+          <t>60,78; 80,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30,52; 50,13</t>
+          <t>31,37; 49,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,43; 46,29</t>
+          <t>28,21; 47,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,73; 37,24</t>
+          <t>18,76; 36,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>74,23; 91,11</t>
+          <t>75,24; 91,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34,98; 48,19</t>
+          <t>34,63; 47,81</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30,5; 45,36</t>
+          <t>31,21; 44,86</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25,31; 38,56</t>
+          <t>24,01; 37,92</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>71,91; 83,94</t>
+          <t>71,62; 83,92</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29,55; 36,3</t>
+          <t>29,57; 36,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32,1; 39,38</t>
+          <t>32,1; 39,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,11; 37,7</t>
+          <t>30,82; 37,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74,24; 81,28</t>
+          <t>74,65; 81,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,88; 40,4</t>
+          <t>33,95; 40,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,35; 38,25</t>
+          <t>31,76; 38,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,89; 36,34</t>
+          <t>29,91; 36,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>70,93; 78,56</t>
+          <t>70,94; 78,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>32,74; 37,39</t>
+          <t>32,82; 37,72</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32,78; 37,72</t>
+          <t>32,91; 37,66</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31,47; 36,29</t>
+          <t>31,45; 36,07</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73,82; 79,19</t>
+          <t>73,51; 78,69</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13299; 26064</t>
+          <t>14015; 25848</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15449; 27052</t>
+          <t>14709; 27387</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17696; 29685</t>
+          <t>17074; 30698</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>70602; 86223</t>
+          <t>71373; 85790</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14956; 27588</t>
+          <t>14906; 27497</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12690; 25125</t>
+          <t>12457; 25421</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19879; 32922</t>
+          <t>19462; 33340</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>83193; 109415</t>
+          <t>84582; 109183</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32450; 49576</t>
+          <t>32078; 49292</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30671; 47388</t>
+          <t>30901; 48307</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40768; 60208</t>
+          <t>40256; 59479</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>160280; 189648</t>
+          <t>160795; 189510</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19400; 32930</t>
+          <t>19150; 32848</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17391; 30613</t>
+          <t>16908; 29993</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18574; 32531</t>
+          <t>18857; 31598</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65601; 79176</t>
+          <t>65279; 79197</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23525; 36297</t>
+          <t>22481; 35956</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14675; 26840</t>
+          <t>14303; 27067</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21774; 36008</t>
+          <t>21878; 36293</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72373; 86266</t>
+          <t>72164; 85496</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45834; 64548</t>
+          <t>46191; 64535</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36461; 54163</t>
+          <t>36340; 54193</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44829; 64072</t>
+          <t>43190; 63272</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>141893; 160260</t>
+          <t>143394; 161502</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9770; 20705</t>
+          <t>9969; 20844</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19141; 31823</t>
+          <t>19076; 31796</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9119; 19599</t>
+          <t>9273; 19760</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38749; 47718</t>
+          <t>39872; 48108</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17602; 29965</t>
+          <t>17916; 30233</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14686; 27378</t>
+          <t>15298; 27444</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14789; 25623</t>
+          <t>14418; 26224</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>42432; 55609</t>
+          <t>43438; 55761</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30822; 46674</t>
+          <t>30627; 48097</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36907; 54766</t>
+          <t>37333; 54865</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26720; 42010</t>
+          <t>26044; 42474</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>85585; 101485</t>
+          <t>84647; 101122</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41862; 60842</t>
+          <t>41356; 60412</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42684; 60812</t>
+          <t>41364; 59845</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49146; 68986</t>
+          <t>49339; 69458</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>156476; 188648</t>
+          <t>156806; 188748</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45781; 64270</t>
+          <t>45625; 66132</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>55228; 74936</t>
+          <t>55890; 76403</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43552; 62829</t>
+          <t>43307; 62622</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>152513; 180473</t>
+          <t>150658; 179432</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93172; 119356</t>
+          <t>91968; 117933</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>103082; 130543</t>
+          <t>102869; 130614</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>97390; 125286</t>
+          <t>97305; 125550</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>317760; 361723</t>
+          <t>317345; 360141</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17927; 31103</t>
+          <t>18449; 30624</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20815; 35434</t>
+          <t>20587; 35312</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29599; 44873</t>
+          <t>29609; 44655</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85994; 100444</t>
+          <t>85960; 100818</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>30316; 45130</t>
+          <t>30967; 45594</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28863; 44697</t>
+          <t>29716; 45593</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35025; 51724</t>
+          <t>34972; 52036</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>85848; 120495</t>
+          <t>83058; 120671</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>52682; 71884</t>
+          <t>52317; 72374</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54250; 74993</t>
+          <t>54846; 75207</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69055; 92285</t>
+          <t>69894; 92601</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>172144; 216532</t>
+          <t>176288; 217892</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>24634; 38029</t>
+          <t>24320; 38423</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14874; 26431</t>
+          <t>14949; 26707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15361; 27802</t>
+          <t>15596; 28063</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42261; 54980</t>
+          <t>41878; 55260</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22095; 36290</t>
+          <t>22708; 35691</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20307; 34275</t>
+          <t>20889; 34991</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13379; 25256</t>
+          <t>12721; 25001</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>53449; 65601</t>
+          <t>54176; 66134</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>51518; 70965</t>
+          <t>50996; 70405</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39020; 58032</t>
+          <t>39933; 57396</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32437; 49423</t>
+          <t>30777; 48592</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>101318; 118273</t>
+          <t>100918; 118236</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>148553; 182448</t>
+          <t>148630; 184110</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>153090; 187837</t>
+          <t>153097; 186219</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>163061; 197570</t>
+          <t>161513; 196742</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>488587; 534937</t>
+          <t>491320; 536653</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>179082; 213526</t>
+          <t>179464; 214454</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>168473; 205540</t>
+          <t>170639; 207829</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>170411; 207208</t>
+          <t>170564; 207289</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>531423; 588572</t>
+          <t>531517; 589345</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>337585; 385610</t>
+          <t>338454; 388952</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>332509; 382626</t>
+          <t>333783; 381990</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>344329; 397121</t>
+          <t>344168; 394720</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1038982; 1114522</t>
+          <t>1034504; 1107502</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29,48%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24,75%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>33,1%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>75,06%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>24,15%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>34,34%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>36,07%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>75,93%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>29,48%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24,75%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>33,1%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,42; 32,13</t>
+          <t>21,11; 38,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,03; 44,74</t>
+          <t>17,41; 33,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,34; 47,35</t>
+          <t>24,06; 42,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68,32; 82,13</t>
+          <t>68,07; 81,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,81; 38,38</t>
+          <t>16,32; 32,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,97; 34,63</t>
+          <t>23,86; 43,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,87; 42,6</t>
+          <t>25,89; 46,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>61,78; 79,75</t>
+          <t>67,5; 82,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,09; 32,41</t>
+          <t>21,41; 32,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,95; 35,88</t>
+          <t>23,39; 36,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,13; 41,57</t>
+          <t>27,83; 40,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,62; 78,51</t>
+          <t>69,95; 79,86</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>43,7%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>30,29%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>30,88%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83,63%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>37,4%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>36,59%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>30,17%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>77,09%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>43,7%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>30,29%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>30,88%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83,41%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,88; 47,82</t>
+          <t>34,71; 53,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,86; 45,88</t>
+          <t>22,52; 41,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,91; 38,39</t>
+          <t>22,84; 38,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68,95; 83,65</t>
+          <t>76,12; 89,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,31; 53,28</t>
+          <t>28,64; 47,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,87; 39,5</t>
+          <t>27,29; 46,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,51; 39,0</t>
+          <t>22,0; 38,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>75,51; 89,46</t>
+          <t>68,96; 83,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,92; 47,39</t>
+          <t>34,24; 46,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,14; 40,47</t>
+          <t>26,65; 40,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24,63; 36,08</t>
+          <t>25,47; 37,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>75,37; 84,89</t>
+          <t>74,84; 84,54</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>28,38%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30,26%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32,87%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>78,38%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>25,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>37,59%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>28,21%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>85,38%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>28,38%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>30,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>32,87%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>82,37%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,12; 35,79</t>
+          <t>20,82; 36,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,68; 47,8</t>
+          <t>22,5; 40,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,84; 40,14</t>
+          <t>23,95; 42,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76,88; 92,76</t>
+          <t>67,35; 88,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,34; 36,02</t>
+          <t>16,93; 35,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,51; 40,38</t>
+          <t>27,7; 47,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,63; 42,98</t>
+          <t>19,39; 39,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>68,03; 87,33</t>
+          <t>77,21; 93,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,54; 33,83</t>
+          <t>21,08; 33,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,76; 40,8</t>
+          <t>27,21; 40,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23,63; 38,53</t>
+          <t>24,03; 38,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73,15; 87,39</t>
+          <t>74,52; 88,45</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>37,23%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>40,59%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30,94%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>77,76%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>33,15%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>37,35%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>35,33%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>78,81%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>37,23%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>40,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>30,94%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,74%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,33; 39,93</t>
+          <t>30,95; 43,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,31; 43,85</t>
+          <t>33,98; 46,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,76; 41,89</t>
+          <t>25,73; 36,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>71,66; 86,26</t>
+          <t>71,5; 83,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,71; 44,51</t>
+          <t>27,23; 39,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,64; 47,35</t>
+          <t>31,52; 44,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,34; 36,65</t>
+          <t>29,23; 41,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>69,02; 82,21</t>
+          <t>71,94; 82,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,67; 39,33</t>
+          <t>30,99; 39,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34,54; 43,85</t>
+          <t>34,74; 43,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,9; 37,29</t>
+          <t>28,84; 36,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72,6; 82,39</t>
+          <t>73,03; 81,28</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>45,32%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39,67%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43,91%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>67,2%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>34,74%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>29,48%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>36,48%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>78,61%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>45,32%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>39,67%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>43,91%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>72,23%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,69; 44,3</t>
+          <t>37,09; 53,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,03; 37,79</t>
+          <t>31,61; 48,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,15; 43,96</t>
+          <t>35,57; 51,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71,98; 84,42</t>
+          <t>54,03; 74,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>36,63; 53,94</t>
+          <t>26,39; 44,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,3; 49,55</t>
+          <t>22,73; 38,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,27; 52,48</t>
+          <t>29,04; 44,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>51,08; 74,21</t>
+          <t>71,81; 83,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34,05; 47,1</t>
+          <t>34,35; 46,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,57; 40,55</t>
+          <t>28,72; 40,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34,82; 46,13</t>
+          <t>34,75; 45,85</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,5; 77,25</t>
+          <t>64,41; 77,26</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>40,27%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>36,64%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27,13%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>86,21%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>42,47%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>38,2%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>35,49%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>72,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>40,27%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>36,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>27,13%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>79,09%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32,48; 51,32</t>
+          <t>31,44; 50,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,73; 49,54</t>
+          <t>28,63; 47,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,85; 46,51</t>
+          <t>19,45; 37,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60,78; 80,21</t>
+          <t>77,39; 92,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31,37; 49,3</t>
+          <t>32,67; 51,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,21; 47,26</t>
+          <t>28,13; 48,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,76; 36,86</t>
+          <t>25,32; 45,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>75,24; 91,85</t>
+          <t>61,8; 81,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34,63; 47,81</t>
+          <t>34,9; 48,15</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31,21; 44,86</t>
+          <t>30,57; 44,34</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24,01; 37,92</t>
+          <t>24,41; 38,42</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>71,62; 83,92</t>
+          <t>72,23; 84,08</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>37,31%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>35,11%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>33,23%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>76,68%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>32,95%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>35,45%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>34,18%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>77,87%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>37,31%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>35,11%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>33,23%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>77,06%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29,57; 36,63</t>
+          <t>33,89; 40,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32,1; 39,04</t>
+          <t>31,71; 38,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30,82; 37,54</t>
+          <t>30,26; 36,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74,65; 81,54</t>
+          <t>72,65; 79,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,95; 40,57</t>
+          <t>29,94; 36,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,76; 38,68</t>
+          <t>31,76; 39,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,91; 36,35</t>
+          <t>30,85; 37,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>70,94; 78,66</t>
+          <t>74,64; 80,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>32,82; 37,72</t>
+          <t>32,84; 37,47</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32,91; 37,66</t>
+          <t>32,62; 37,64</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31,45; 36,07</t>
+          <t>31,38; 36,05</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73,51; 78,69</t>
+          <t>74,71; 79,51</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>121</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21119</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18173</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25899</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>92003</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>19426</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>21023</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>23384</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>79319</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>21119</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18173</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>25899</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>98604</t>
+          <t>77344</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>177923</t>
+          <t>169348</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14015; 25848</t>
+          <t>15125; 27595</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14709; 27387</t>
+          <t>12784; 24916</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17074; 30698</t>
+          <t>18831; 33401</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71373; 85790</t>
+          <t>83435; 100187</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14906; 27497</t>
+          <t>13130; 26454</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12457; 25421</t>
+          <t>14606; 26919</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19462; 33340</t>
+          <t>16783; 30159</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84582; 109183</t>
+          <t>69480; 84581</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32078; 49292</t>
+          <t>32567; 50004</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30901; 48307</t>
+          <t>31493; 49329</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40256; 59479</t>
+          <t>39823; 58337</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>160795; 189510</t>
+          <t>157729; 180076</t>
         </is>
       </c>
     </row>
@@ -1999,37 +1999,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>29490</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20758</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28739</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>76432</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>25691</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>23922</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>24831</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>72994</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>29490</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>20758</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>28739</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>79718</t>
+          <t>74424</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>152711</t>
+          <t>150856</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19150; 32848</t>
+          <t>23424; 35805</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16908; 29993</t>
+          <t>15432; 28218</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18857; 31598</t>
+          <t>21260; 36281</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65279; 79197</t>
+          <t>69571; 81853</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22481; 35956</t>
+          <t>19669; 32810</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14303; 27067</t>
+          <t>17839; 30663</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21878; 36293</t>
+          <t>18111; 31922</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72164; 85496</t>
+          <t>66580; 80762</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46191; 64535</t>
+          <t>46631; 63986</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36340; 54193</t>
+          <t>35683; 53601</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43190; 63272</t>
+          <t>44662; 64963</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>143394; 161502</t>
+          <t>140660; 158895</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>64</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>23826</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20568</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>20052</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>44629</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>14562</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>25004</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>13888</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>44280</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>23826</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>20568</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>20052</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50210</t>
+          <t>46324</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94489</t>
+          <t>90954</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9969; 20844</t>
+          <t>17480; 30784</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19076; 31796</t>
+          <t>15290; 27586</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9273; 19760</t>
+          <t>14615; 25841</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39872; 48108</t>
+          <t>38350; 50165</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17916; 30233</t>
+          <t>9864; 20488</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15298; 27444</t>
+          <t>18427; 31762</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14418; 26224</t>
+          <t>9545; 19419</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43438; 55761</t>
+          <t>41295; 49967</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30627; 48097</t>
+          <t>29979; 47845</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37333; 54865</t>
+          <t>36599; 55126</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26044; 42474</t>
+          <t>26484; 42505</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84647; 101122</t>
+          <t>82291; 97674</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>215</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>55314</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>65501</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>52875</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>157036</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>50150</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>50980</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>58569</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>172457</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>55314</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>65501</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>52875</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>167540</t>
+          <t>139617</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>339997</t>
+          <t>296652</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41356; 60412</t>
+          <t>45980; 63897</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41364; 59845</t>
+          <t>54830; 75802</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49339; 69458</t>
+          <t>43968; 62722</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>156806; 188748</t>
+          <t>144397; 167991</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45625; 66132</t>
+          <t>41199; 60244</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>55890; 76403</t>
+          <t>43015; 61315</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43307; 62622</t>
+          <t>48457; 68787</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>150658; 179432</t>
+          <t>129243; 148956</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>91968; 117933</t>
+          <t>92918; 119038</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>102869; 130614</t>
+          <t>103469; 130015</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>97305; 125550</t>
+          <t>97090; 124126</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>317345; 360141</t>
+          <t>278693; 310164</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>140</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>38312</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>36496</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>43533</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>99617</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>24012</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>27548</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>37060</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>93877</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>38312</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>36496</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>43533</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>107800</t>
+          <t>93213</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>201677</t>
+          <t>192830</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18449; 30624</t>
+          <t>31356; 45486</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20587; 35312</t>
+          <t>29084; 44218</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29609; 44655</t>
+          <t>35272; 50919</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85960; 100818</t>
+          <t>80095; 110415</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>30967; 45594</t>
+          <t>18245; 30513</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29716; 45593</t>
+          <t>21244; 36067</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34972; 52036</t>
+          <t>29503; 45336</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>83058; 120671</t>
+          <t>85265; 99596</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>52317; 72374</t>
+          <t>52778; 71346</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54846; 75207</t>
+          <t>53271; 75170</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69894; 92601</t>
+          <t>69749; 92032</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>176288; 217892</t>
+          <t>171948; 206252</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>71</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>29149</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>27130</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>18403</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>58871</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>31794</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>20594</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>21413</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>49603</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>29149</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>27130</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>18403</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>61068</t>
+          <t>50788</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>110671</t>
+          <t>109660</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>24320; 38423</t>
+          <t>22758; 36198</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14949; 26707</t>
+          <t>21197; 34888</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15596; 28063</t>
+          <t>13191; 25625</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41878; 55260</t>
+          <t>52846; 63076</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22708; 35691</t>
+          <t>24459; 38702</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20889; 34991</t>
+          <t>15167; 26341</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12721; 25001</t>
+          <t>15278; 27532</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>54176; 66134</t>
+          <t>43481; 57063</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>50996; 70405</t>
+          <t>51398; 70904</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39933; 57396</t>
+          <t>39114; 56727</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30777; 48592</t>
+          <t>31287; 49243</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>100918; 118236</t>
+          <t>100149; 116576</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>241</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>266</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>721</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>748</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>197211</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>188626</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>189502</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>528588</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>165636</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>169071</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>179144</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>512530</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>197211</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>188626</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>189502</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>564939</t>
+          <t>481711</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1077469</t>
+          <t>1010300</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>148630; 184110</t>
+          <t>179147; 213532</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>153097; 186219</t>
+          <t>170363; 207597</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>161513; 196742</t>
+          <t>172554; 209016</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>491320; 536653</t>
+          <t>500871; 548690</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>179464; 214454</t>
+          <t>150479; 183721</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>170639; 207829</t>
+          <t>151473; 186786</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>170564; 207289</t>
+          <t>161691; 197605</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>531517; 589345</t>
+          <t>464058; 497713</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>338454; 388952</t>
+          <t>338633; 386429</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>333783; 381990</t>
+          <t>330835; 381800</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>344168; 394720</t>
+          <t>343426; 394457</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1034504; 1107502</t>
+          <t>979470; 1042418</t>
         </is>
       </c>
     </row>
